--- a/data/trans_orig/P16A20_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>273240</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>140726</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>411954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>413966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>220997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171629</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173576</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>392563</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>394572</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75234</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77179</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>396220</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>676951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>678938</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>330128</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1007066</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1009066</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>215800</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217809</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>423026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240927</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>242798</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>458409</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>460305</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>701212</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>703103</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1942247</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1944238</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1397753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1399722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3341977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3343960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>220157</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222149</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>120013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122122</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>342231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>344271</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206228</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208377</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>119653</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121718</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>327969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276482</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278461</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82739</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84769</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>361232</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>546771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>548793</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>246870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248911</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>795673</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>797704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>252708</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184298</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>434970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185320</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>292774</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>294780</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>478130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>480099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1693794</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1695807</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1054534</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1056598</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2750371</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2752404</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>200107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>202181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>154796</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>354962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356977</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188303</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160783</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>351074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>228678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>230681</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49892</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>278579</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>280573</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>550183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>552187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342266</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>344192</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>894403</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>896379</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>306349</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>308383</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205612</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>511997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>513995</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214757</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216766</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>324394</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>326333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>541128</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1696470</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1698501</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1241649</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1243597</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2940101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2942097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52377</t>
+          <t>51472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34798</t>
+          <t>35132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57264</t>
+          <t>56534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495070</t>
+          <t>495241</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503028</t>
+          <t>503177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>395090</t>
+          <t>395995</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>416614</t>
+          <t>416461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>895415</t>
+          <t>896145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>917881</t>
+          <t>917547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>38473</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26137</t>
+          <t>25528</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45406</t>
+          <t>44316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441154</t>
+          <t>441668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>450391</t>
+          <t>450451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344189</t>
+          <t>344107</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361230</t>
+          <t>361166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>789387</t>
+          <t>790477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>808656</t>
+          <t>809265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21872</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>28973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660679</t>
+          <t>659861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145039</t>
+          <t>145384</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157217</t>
+          <t>156798</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>806805</t>
+          <t>806202</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828781</t>
+          <t>828291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>27438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79454</t>
+          <t>78458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>579035</t>
+          <t>617546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89025</t>
+          <t>89000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>761705</t>
+          <t>799313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1007635</t>
+          <t>1007381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1023710</t>
+          <t>1024271</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>398135</t>
+          <t>359624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>897716</t>
+          <t>898712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1250284</t>
+          <t>1212676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922964</t>
+          <t>1922989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52311</t>
+          <t>53400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92281</t>
+          <t>94006</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62528</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100357</t>
+          <t>99345</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>457484</t>
+          <t>458462</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469976</t>
+          <t>470458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>746715</t>
+          <t>744990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>786685</t>
+          <t>785596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1212688</t>
+          <t>1213700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1250517</t>
+          <t>1249684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>18613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39175</t>
+          <t>39539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>63111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41209</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68502</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220468</t>
+          <t>221894</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>698601</t>
+          <t>696394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>720330</t>
+          <t>719966</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>931510</t>
+          <t>928900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958803</t>
+          <t>958919</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29209</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59059</t>
+          <t>59087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>275972</t>
+          <t>278111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1060708</t>
+          <t>1126475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>313081</t>
+          <t>311924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1185963</t>
+          <t>1268785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3316005</t>
+          <t>3315977</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3345855</t>
+          <t>3345559</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2511921</t>
+          <t>2446154</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3296657</t>
+          <t>3294518</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5761730</t>
+          <t>5678908</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6634612</t>
+          <t>6635769</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A20_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Clase-trans_orig.xlsx
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8633,27 +8633,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51472</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44764</t>
+          <t>49145</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35132</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56534</t>
+          <t>62025</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -8746,22 +8746,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>500183</t>
+          <t>545061</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495241</t>
+          <t>539781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503177</t>
+          <t>548302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>407732</t>
+          <t>444823</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>395995</t>
+          <t>433337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>416461</t>
+          <t>455292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>907915</t>
+          <t>989884</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>896145</t>
+          <t>977004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>917547</t>
+          <t>1000280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,22 +8976,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4989</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29192</t>
+          <t>32975</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38473</t>
+          <t>43491</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34182</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25528</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44316</t>
+          <t>48551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -9089,27 +9089,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>447224</t>
+          <t>478254</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>441668</t>
+          <t>472024</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>450451</t>
+          <t>481312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>353388</t>
+          <t>390168</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344107</t>
+          <t>379652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361166</t>
+          <t>398208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>800611</t>
+          <t>868422</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>790477</t>
+          <t>857804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>809265</t>
+          <t>877713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15392</t>
+          <t>17063</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21527</t>
+          <t>24134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17913</t>
+          <t>19497</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28973</t>
+          <t>27686</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>665743</t>
+          <t>469178</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659861</t>
+          <t>464921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>470838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>151519</t>
+          <t>170434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145384</t>
+          <t>163363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156798</t>
+          <t>175945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>817262</t>
+          <t>639612</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>806202</t>
+          <t>631423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828291</t>
+          <t>645627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>271520</t>
+          <t>74743</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78458</t>
+          <t>62130</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>617546</t>
+          <t>88161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>289013</t>
+          <t>92893</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89000</t>
+          <t>77252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>799313</t>
+          <t>109066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1017326</t>
+          <t>1113693</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1007381</t>
+          <t>1104504</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1024271</t>
+          <t>1119960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>705650</t>
+          <t>785494</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359624</t>
+          <t>772076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>898712</t>
+          <t>798107</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1722976</t>
+          <t>1899186</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1212676</t>
+          <t>1883013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1922989</t>
+          <t>1914827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977170</t>
+          <t>860237</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977170</t>
+          <t>860237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977170</t>
+          <t>860237</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011989</t>
+          <t>1992079</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011989</t>
+          <t>1992079</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011989</t>
+          <t>1992079</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>9187</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>71968</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53400</t>
+          <t>63274</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94006</t>
+          <t>88721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>79925</t>
+          <t>83762</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63361</t>
+          <t>70010</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99345</t>
+          <t>99174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>466092</t>
+          <t>557789</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458462</t>
+          <t>549263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470458</t>
+          <t>562577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>767028</t>
+          <t>755552</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>744990</t>
+          <t>741406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>785596</t>
+          <t>766853</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1233120</t>
+          <t>1313341</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1213700</t>
+          <t>1297929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1249684</t>
+          <t>1327093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48813</t>
+          <t>56634</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39539</t>
+          <t>43743</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63111</t>
+          <t>69432</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>52636</t>
+          <t>60025</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41093</t>
+          <t>48123</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71112</t>
+          <t>75902</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236684</t>
+          <t>233838</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221894</t>
+          <t>219664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>710692</t>
+          <t>785635</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>696394</t>
+          <t>772837</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>719966</t>
+          <t>798526</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>947376</t>
+          <t>1019472</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>928900</t>
+          <t>1003595</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958919</t>
+          <t>1031374</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759505</t>
+          <t>842269</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759505</t>
+          <t>842269</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759505</t>
+          <t>842269</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000012</t>
+          <t>1079497</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000012</t>
+          <t>1079497</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000012</t>
+          <t>1079497</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41811</t>
+          <t>43676</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59087</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>476622</t>
+          <t>299578</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>278111</t>
+          <t>273207</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1126475</t>
+          <t>332094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>518433</t>
+          <t>343255</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>311924</t>
+          <t>312850</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1268785</t>
+          <t>376288</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3333253</t>
+          <t>3397812</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3315977</t>
+          <t>3382997</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3345559</t>
+          <t>3410170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3096007</t>
+          <t>3332106</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2446154</t>
+          <t>3299590</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3294518</t>
+          <t>3358477</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6429260</t>
+          <t>6729917</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5678908</t>
+          <t>6696884</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6635769</t>
+          <t>6760322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3375064</t>
+          <t>3441488</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572629</t>
+          <t>3631684</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572629</t>
+          <t>3631684</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572629</t>
+          <t>3631684</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947693</t>
+          <t>7073172</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947693</t>
+          <t>7073172</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947693</t>
+          <t>7073172</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
